--- a/event_planner_forms/002_gift_basket_order_form_template--event_planner_forms.xlsx
+++ b/event_planner_forms/002_gift_basket_order_form_template--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>gift_card_details</t>
+          <t>gift_card_details_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Gift Card Details</t>
+          <t>Gift Card Details 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>gift_basket_price</t>
+          <t>gift_basket_price_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gift Basket Price</t>
+          <t>Gift Basket Price 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>gift_basket_total</t>
+          <t>gift_basket_total_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gift Basket Total</t>
+          <t>Gift Basket Total 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,7 +980,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gift_shipping</t>
+          <t>gift_shipping_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1029,7 +1029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1589,129 +1589,61 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>gift_card_expiration_year_choices</t>
+          <t>gift_basket_price_range_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>10_-_20</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>10 - 20</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>gift_card_expiration_year_choices</t>
+          <t>gift_basket_price_range_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>21_-_30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>21 - 30</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>gift_card_expiration_year_choices</t>
+          <t>gift_basket_price_range_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>31_-_40</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>gift_card_expiration_year_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>gift_basket_price_range_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>10_-_20</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>10 - 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>gift_basket_price_range_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>21_-_30</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>21 - 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>gift_basket_price_range_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>31_-_40</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
         <is>
           <t>31 - 40</t>
         </is>
